--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>

--- a/api/xlsx/fr/FileFormat.xlsx
+++ b/api/xlsx/fr/FileFormat.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>application/1d-interleaved-parityfec</t>
